--- a/Result/profitability/2201.xlsx
+++ b/Result/profitability/2201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45</v>
+        <v>0.3162499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>29.6425</v>
+        <v>29.72375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.275</v>
+        <v>0.2224999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>27.44875</v>
+        <v>27.9475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1862499999999999</v>
+        <v>0.1524999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>25.42875</v>
+        <v>25.22</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1412499999999999</v>
+        <v>0.1462499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>23.10375</v>
+        <v>23.04125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.145</v>
+        <v>0.13375</v>
       </c>
       <c r="N6" t="n">
-        <v>21.1875</v>
+        <v>21.275</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1462499999999999</v>
+        <v>0.145</v>
       </c>
       <c r="N7" t="n">
-        <v>19.29375</v>
+        <v>19.59125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1799999999999999</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.6625</v>
+        <v>17.60375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1237499999999999</v>
+        <v>0.12375</v>
       </c>
       <c r="N9" t="n">
         <v>15.16375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17394</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11737</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5657</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1797</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-408</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1389</v>
+      </c>
+      <c r="K75" t="n">
+        <v>157</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4024999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.885</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4699999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01424674143679905</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.03999999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3636363636363635</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01514233797698361</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
